--- a/Data/EC/NIT-9007164287.xlsx
+++ b/Data/EC/NIT-9007164287.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F92CCB65-1689-444A-B0C7-041B14CBE398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF668C34-039A-4429-ABE1-241550987A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B3B3A67F-BAF3-4C70-AB2B-7C8CE8BF3613}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0DA26071-98A4-4089-9357-BB383F09A172}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="119">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,277 +71,295 @@
     <t>JUAN LUIS OSORNO GUERRERO</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
     <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -440,9 +458,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -455,7 +471,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -655,23 +673,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -699,10 +717,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -740,22 +758,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69531677-9B0B-D826-7DD6-6E0497E86064}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AB9FA71-8D31-EDE1-93CA-58BCF7CD3A8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -777,7 +795,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1106,27 +1124,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA0B785-788E-47AC-BFBD-E861EBBF6E8D}">
-  <dimension ref="B2:J112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F39B0B-8591-4532-AB6C-521A4B1F1886}">
+  <dimension ref="B2:J118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1135,7 +1153,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1146,7 +1164,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1157,7 +1175,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1168,10 +1186,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1184,8 +1202,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1200,15 +1218,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2817962</v>
+        <v>3005456</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1216,27 +1234,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F13" s="5">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1256,16 +1274,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1297,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1288,7 +1306,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1302,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1311,7 +1329,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1343,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1334,7 +1352,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1366,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1357,7 +1375,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1371,7 +1389,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1380,7 +1398,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1412,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1403,7 +1421,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1435,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1426,7 +1444,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1449,7 +1467,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1472,7 +1490,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1495,7 +1513,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1518,7 +1536,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1541,7 +1559,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1564,7 +1582,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1587,7 +1605,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1610,7 +1628,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1633,7 +1651,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1674,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1697,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1720,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1743,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1748,7 +1766,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1789,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1812,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1817,7 +1835,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1858,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1863,7 +1881,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +1904,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1909,7 +1927,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1932,7 +1950,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1955,7 +1973,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1978,7 +1996,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2019,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2024,7 +2042,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2047,7 +2065,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2070,7 +2088,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2093,7 +2111,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2116,7 +2134,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2139,7 +2157,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2162,7 +2180,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2185,7 +2203,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2208,7 +2226,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2231,7 +2249,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2254,7 +2272,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2277,7 +2295,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2300,7 +2318,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2323,7 +2341,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2346,7 +2364,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2369,7 +2387,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2392,7 +2410,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2415,7 +2433,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2438,7 +2456,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2461,7 +2479,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2484,7 +2502,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2507,7 +2525,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2530,7 +2548,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2553,7 +2571,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2576,7 +2594,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2599,7 +2617,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2622,7 +2640,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2645,7 +2663,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2668,7 +2686,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2691,7 +2709,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2714,7 +2732,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2737,7 +2755,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2760,7 +2778,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2783,7 +2801,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2806,7 +2824,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2829,7 +2847,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2852,7 +2870,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2875,7 +2893,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2898,7 +2916,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2921,7 +2939,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2944,7 +2962,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2967,7 +2985,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2990,7 +3008,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3013,7 +3031,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3036,7 +3054,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3059,7 +3077,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3082,7 +3100,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +3123,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3128,7 +3146,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3151,7 +3169,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3174,7 +3192,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3197,7 +3215,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3220,7 +3238,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3243,7 +3261,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3266,7 +3284,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3289,7 +3307,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3312,7 +3330,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3335,57 +3353,195 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B106" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="22" t="s">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F106" s="24">
-        <v>31249</v>
-      </c>
-      <c r="G106" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H106" s="25"/>
-      <c r="I106" s="25"/>
-      <c r="J106" s="26"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B111" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C111" s="32"/>
-      <c r="H111" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B112" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C112" s="32"/>
-      <c r="H112" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
+      <c r="F106" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G106" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H106" s="19"/>
+      <c r="I106" s="19"/>
+      <c r="J106" s="20"/>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B107" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F107" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G107" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H107" s="19"/>
+      <c r="I107" s="19"/>
+      <c r="J107" s="20"/>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F108" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G108" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="20"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F109" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G109" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="20"/>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B110" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F110" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G110" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="20"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F111" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G111" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="20"/>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B112" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F112" s="24">
+        <v>27578</v>
+      </c>
+      <c r="G112" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H112" s="25"/>
+      <c r="I112" s="25"/>
+      <c r="J112" s="26"/>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B117" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C117" s="32"/>
+      <c r="H117" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B118" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C118" s="32"/>
+      <c r="H118" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="H112:J112"/>
-    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="H118:J118"/>
+    <mergeCell ref="H117:J117"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
